--- a/output/tables/table.dimensions.xlsx
+++ b/output/tables/table.dimensions.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uccl0-my.sharepoint.com/personal/jciturra_uc_cl/Documents/papers/factorial-cohesion/output/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="169" documentId="11_F25DC773A252ABDACC10489661DA46A85ADE58E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AED38A7F-1C94-4420-BBC6-3AF43A1CE9AF}"/>
+  <xr:revisionPtr revIDLastSave="390" documentId="11_F25DC773A252ABDACC10489661DA46A85ADE58E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{274D91F1-ECA3-41C3-85A5-27AC97720C4C}"/>
   <bookViews>
-    <workbookView xWindow="14400" yWindow="450" windowWidth="14400" windowHeight="15750" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="116">
   <si>
     <t>Dimension</t>
   </si>
@@ -284,13 +285,121 @@
   </si>
   <si>
     <t>Conflict</t>
+  </si>
+  <si>
+    <t>Objective</t>
+  </si>
+  <si>
+    <t>Vertical</t>
+  </si>
+  <si>
+    <t>Subjective</t>
+  </si>
+  <si>
+    <t>Class identity</t>
+  </si>
+  <si>
+    <t>Social Positions</t>
+  </si>
+  <si>
+    <t>Political ideology</t>
+  </si>
+  <si>
+    <t>Horizontal</t>
+  </si>
+  <si>
+    <t>Social Cohesion</t>
+  </si>
+  <si>
+    <t>Interpersonal networks</t>
+  </si>
+  <si>
+    <t>Institutional affiliation</t>
+  </si>
+  <si>
+    <t>Generalized Trust</t>
+  </si>
+  <si>
+    <t>Voluntary association</t>
+  </si>
+  <si>
+    <t>Electoral participation</t>
+  </si>
+  <si>
+    <t>Subjective social status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Socioeconomic </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sociocultural </t>
+  </si>
+  <si>
+    <t>Socioeconomic perception</t>
+  </si>
+  <si>
+    <t>Political-values</t>
+  </si>
+  <si>
+    <t>Nationality, migration</t>
+  </si>
+  <si>
+    <t>Table: Dimensions of social positions and social cohesion</t>
+  </si>
+  <si>
+    <t>Institutonal Trust</t>
+  </si>
+  <si>
+    <t>Political Trust</t>
+  </si>
+  <si>
+    <t>Interpersonal association</t>
+  </si>
+  <si>
+    <t>Interpersonal expectation</t>
+  </si>
+  <si>
+    <t>Societal association</t>
+  </si>
+  <si>
+    <t>Societal expectation</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Social Class</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Note: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Own elaboration. </t>
+    </r>
+  </si>
+  <si>
+    <t>Group-based Trust</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -328,6 +437,32 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -409,7 +544,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -449,6 +584,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -460,8 +598,28 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -478,10 +636,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -781,7 +935,7 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="16" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="8" t="s">
@@ -798,7 +952,7 @@
       </c>
     </row>
     <row r="5" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="15"/>
+      <c r="A5" s="16"/>
       <c r="B5" s="9" t="s">
         <v>6</v>
       </c>
@@ -813,7 +967,7 @@
       </c>
     </row>
     <row r="6" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="16"/>
+      <c r="A6" s="17"/>
       <c r="B6" s="9" t="s">
         <v>8</v>
       </c>
@@ -828,7 +982,7 @@
       </c>
     </row>
     <row r="7" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="18" t="s">
         <v>10</v>
       </c>
       <c r="B7" s="9" t="s">
@@ -845,7 +999,7 @@
       </c>
     </row>
     <row r="8" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="15"/>
+      <c r="A8" s="16"/>
       <c r="B8" s="9" t="s">
         <v>6</v>
       </c>
@@ -860,7 +1014,7 @@
       </c>
     </row>
     <row r="9" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="16"/>
+      <c r="A9" s="17"/>
       <c r="B9" s="9" t="s">
         <v>8</v>
       </c>
@@ -875,7 +1029,7 @@
       </c>
     </row>
     <row r="10" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="17" t="s">
+      <c r="A10" s="18" t="s">
         <v>14</v>
       </c>
       <c r="B10" s="9" t="s">
@@ -892,7 +1046,7 @@
       </c>
     </row>
     <row r="11" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="15"/>
+      <c r="A11" s="16"/>
       <c r="B11" s="9" t="s">
         <v>16</v>
       </c>
@@ -907,7 +1061,7 @@
       </c>
     </row>
     <row r="12" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="16"/>
+      <c r="A12" s="17"/>
       <c r="B12" s="9" t="s">
         <v>18</v>
       </c>
@@ -922,7 +1076,7 @@
       </c>
     </row>
     <row r="13" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="17" t="s">
+      <c r="A13" s="18" t="s">
         <v>19</v>
       </c>
       <c r="B13" s="9" t="s">
@@ -939,7 +1093,7 @@
       </c>
     </row>
     <row r="14" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="15"/>
+      <c r="A14" s="16"/>
       <c r="B14" s="9" t="s">
         <v>22</v>
       </c>
@@ -954,7 +1108,7 @@
       </c>
     </row>
     <row r="15" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="15"/>
+      <c r="A15" s="16"/>
       <c r="B15" s="9" t="s">
         <v>24</v>
       </c>
@@ -969,7 +1123,7 @@
       </c>
     </row>
     <row r="16" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="16"/>
+      <c r="A16" s="17"/>
       <c r="B16" s="9" t="s">
         <v>26</v>
       </c>
@@ -984,7 +1138,7 @@
       </c>
     </row>
     <row r="17" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="17" t="s">
+      <c r="A17" s="18" t="s">
         <v>28</v>
       </c>
       <c r="B17" s="9" t="s">
@@ -1001,7 +1155,7 @@
       </c>
     </row>
     <row r="18" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="15"/>
+      <c r="A18" s="16"/>
       <c r="B18" s="8" t="s">
         <v>31</v>
       </c>
@@ -1016,7 +1170,7 @@
       </c>
     </row>
     <row r="19" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="15"/>
+      <c r="A19" s="16"/>
       <c r="B19" s="8" t="s">
         <v>33</v>
       </c>
@@ -1031,7 +1185,7 @@
       </c>
     </row>
     <row r="20" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="16"/>
+      <c r="A20" s="17"/>
       <c r="B20" s="8" t="s">
         <v>35</v>
       </c>
@@ -1046,7 +1200,7 @@
       </c>
     </row>
     <row r="21" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="15" t="s">
+      <c r="A21" s="16" t="s">
         <v>37</v>
       </c>
       <c r="B21" s="9" t="s">
@@ -1063,7 +1217,7 @@
       </c>
     </row>
     <row r="22" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="15"/>
+      <c r="A22" s="16"/>
       <c r="B22" s="8" t="s">
         <v>40</v>
       </c>
@@ -1078,7 +1232,7 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="15"/>
+      <c r="A23" s="16"/>
       <c r="B23" s="8" t="s">
         <v>42</v>
       </c>
@@ -1093,7 +1247,7 @@
       </c>
     </row>
     <row r="24" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="16"/>
+      <c r="A24" s="17"/>
       <c r="B24" s="9" t="s">
         <v>43</v>
       </c>
@@ -1108,7 +1262,7 @@
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="14" t="s">
+      <c r="A30" s="15" t="s">
         <v>45</v>
       </c>
       <c r="B30" s="3" t="s">
@@ -1125,7 +1279,7 @@
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="14"/>
+      <c r="A31" s="15"/>
       <c r="B31" s="3" t="s">
         <v>47</v>
       </c>
@@ -1140,7 +1294,7 @@
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" s="14" t="s">
+      <c r="A32" s="15" t="s">
         <v>48</v>
       </c>
       <c r="B32" s="3" t="s">
@@ -1157,7 +1311,7 @@
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33" s="14"/>
+      <c r="A33" s="15"/>
       <c r="B33" s="3" t="s">
         <v>51</v>
       </c>
@@ -1172,7 +1326,7 @@
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" s="14"/>
+      <c r="A34" s="15"/>
       <c r="B34" s="3" t="s">
         <v>53</v>
       </c>
@@ -1258,13 +1412,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="D1" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="E1" s="14" t="s">
         <v>85</v>
       </c>
     </row>
@@ -1294,13 +1448,13 @@
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="D7" s="18" t="s">
+      <c r="D7" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="E7" s="18" t="s">
+      <c r="E7" s="14" t="s">
         <v>85</v>
       </c>
     </row>
@@ -1332,4 +1486,226 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DC83454-8B78-4B59-AC4F-A91A3754BF2C}">
+  <dimension ref="A1:G14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.5703125" customWidth="1"/>
+    <col min="5" max="5" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="20"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="19"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="19"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="22"/>
+      <c r="B3" s="23" t="s">
+        <v>90</v>
+      </c>
+      <c r="C3" s="23"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="F3" s="23"/>
+      <c r="G3" s="19"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="24"/>
+      <c r="B4" s="25" t="s">
+        <v>87</v>
+      </c>
+      <c r="C4" s="25" t="s">
+        <v>92</v>
+      </c>
+      <c r="D4" s="25"/>
+      <c r="E4" s="25" t="s">
+        <v>87</v>
+      </c>
+      <c r="F4" s="25" t="s">
+        <v>92</v>
+      </c>
+      <c r="G4" s="19"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="27" t="s">
+        <v>86</v>
+      </c>
+      <c r="B5" s="26" t="s">
+        <v>100</v>
+      </c>
+      <c r="C5" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="D5" s="27"/>
+      <c r="E5" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="F5" s="26" t="s">
+        <v>108</v>
+      </c>
+      <c r="G5" s="19"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="28"/>
+      <c r="B6" s="22" t="s">
+        <v>112</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="28"/>
+      <c r="E6" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="F6" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="G6" s="19"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="28"/>
+      <c r="B7" s="22" t="s">
+        <v>113</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="D7" s="28"/>
+      <c r="E7" s="22" t="s">
+        <v>95</v>
+      </c>
+      <c r="F7" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="G7" s="19"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="B8" s="26" t="s">
+        <v>102</v>
+      </c>
+      <c r="C8" s="26" t="s">
+        <v>103</v>
+      </c>
+      <c r="D8" s="28"/>
+      <c r="E8" s="26" t="s">
+        <v>111</v>
+      </c>
+      <c r="F8" s="26" t="s">
+        <v>109</v>
+      </c>
+      <c r="G8" s="19"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="28"/>
+      <c r="B9" s="22" t="s">
+        <v>99</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>91</v>
+      </c>
+      <c r="D9" s="28"/>
+      <c r="E9" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="F9" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="G9" s="19"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="29"/>
+      <c r="B10" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="C10" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="D10" s="29"/>
+      <c r="E10" s="24" t="s">
+        <v>107</v>
+      </c>
+      <c r="F10" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="G10" s="19"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="22" t="s">
+        <v>114</v>
+      </c>
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="19"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="19"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="19"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="D5:D7"/>
+    <mergeCell ref="A5:A7"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>